--- a/02_DIA_inicio_2026_analisis_assets/rbd_9415_escuela-territorio-antartico_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9415_escuela-territorio-antartico_nt2_rubricas.xlsx
@@ -1776,13 +1776,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4977CC43-FBCD-451A-954E-E5E97563F375}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BB4C483-60B6-4C30-8AD7-4012BBA2A426}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEB41073-8ADF-44B1-850B-260E3BA0F253}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF3ACFA-1391-4A85-9173-E7BD9030AAD6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC1A171F-C7CE-4489-B574-735BD3C5C862}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE626EDD-5A5A-476B-B58C-A7FE07CC0E9B}"/>
 </file>